--- a/AIGGPA_Fieldwork_Review/03_AIGGPA_Master_Coded_DataMatrix.xlsx
+++ b/AIGGPA_Fieldwork_Review/03_AIGGPA_Master_Coded_DataMatrix.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variable_Codebook" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data_Matrix'!$A$1:$CD$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data_Matrix'!$A$1:$CI$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD141"/>
+  <dimension ref="A1:CI155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -548,6 +548,11 @@
     <col width="16" customWidth="1" min="80" max="80"/>
     <col width="16" customWidth="1" min="81" max="81"/>
     <col width="16" customWidth="1" min="82" max="82"/>
+    <col width="16" customWidth="1" min="83" max="83"/>
+    <col width="16" customWidth="1" min="84" max="84"/>
+    <col width="16" customWidth="1" min="85" max="85"/>
+    <col width="16" customWidth="1" min="86" max="86"/>
+    <col width="16" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -943,20 +948,45 @@
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
+          <t>Q77_HealthTools</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Q78_ANMOL_ABHA</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Q79_IHIP_workload</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Q80_ANC_steps</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Q81_Outbreak_report</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
           <t>PU_Mean</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>EE_Mean</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>SI_Mean</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>FC_Internet</t>
         </is>
@@ -984,7 +1014,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -1227,16 +1257,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA2" s="2" t="n">
+      <c r="CF2" s="2" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC2" s="2" t="n">
+      <c r="CG2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH2" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD2" s="2" t="n">
+      <c r="CI2" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1262,7 +1292,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1505,16 +1535,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB3" s="3" t="n">
+      <c r="CF3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG3" s="3" t="n">
         <v>2.33</v>
       </c>
-      <c r="CC3" s="3" t="n">
+      <c r="CH3" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD3" s="3" t="n">
+      <c r="CI3" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1540,7 +1570,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -1783,16 +1813,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA4" s="2" t="n">
+      <c r="CF4" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB4" s="2" t="n">
+      <c r="CG4" s="2" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC4" s="2" t="n">
+      <c r="CH4" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD4" s="2" t="n">
+      <c r="CI4" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1818,7 +1848,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2061,16 +2091,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA5" s="3" t="n">
+      <c r="CF5" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB5" s="3" t="n">
+      <c r="CG5" s="3" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC5" s="3" t="n">
+      <c r="CH5" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD5" s="3" t="n">
+      <c r="CI5" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2096,7 +2126,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -2339,16 +2369,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA6" s="2" t="n">
+      <c r="CF6" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC6" s="2" t="n">
+      <c r="CG6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH6" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD6" s="2" t="n">
+      <c r="CI6" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2374,7 +2404,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2617,16 +2647,16 @@
           <t>Show to senior officer for decision</t>
         </is>
       </c>
-      <c r="CA7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB7" s="3" t="n">
+      <c r="CF7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG7" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC7" s="3" t="n">
+      <c r="CH7" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD7" s="3" t="n">
+      <c r="CI7" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2652,7 +2682,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -2895,16 +2925,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB8" s="2" t="n">
+      <c r="CF8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG8" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC8" s="2" t="n">
+      <c r="CH8" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD8" s="2" t="n">
+      <c r="CI8" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2930,7 +2960,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3173,16 +3203,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB9" s="3" t="n">
+      <c r="CF9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG9" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC9" s="3" t="n">
+      <c r="CH9" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD9" s="3" t="n">
+      <c r="CI9" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3208,7 +3238,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -3451,16 +3481,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC10" s="2" t="n">
+      <c r="CF10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH10" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD10" s="2" t="n">
+      <c r="CI10" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3486,7 +3516,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3729,16 +3759,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD11" s="3" t="n">
+      <c r="CF11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI11" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3764,7 +3794,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -4007,16 +4037,16 @@
           <t>Show to senior officer for decision</t>
         </is>
       </c>
-      <c r="CA12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB12" s="2" t="n">
+      <c r="CF12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG12" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC12" s="2" t="n">
+      <c r="CH12" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD12" s="2" t="n">
+      <c r="CI12" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4042,7 +4072,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -4285,16 +4315,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA13" s="3" t="n">
+      <c r="CF13" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD13" s="3" t="n">
+      <c r="CG13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI13" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4320,7 +4350,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -4563,16 +4593,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA14" s="2" t="n">
+      <c r="CF14" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB14" s="2" t="n">
+      <c r="CG14" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD14" s="2" t="n">
+      <c r="CH14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI14" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4598,7 +4628,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -4841,16 +4871,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA15" s="3" t="n">
+      <c r="CF15" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB15" s="3" t="n">
+      <c r="CG15" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC15" s="3" t="n">
+      <c r="CH15" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD15" s="3" t="n">
+      <c r="CI15" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4876,7 +4906,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -5119,16 +5149,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB16" s="2" t="n">
+      <c r="CF16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG16" s="2" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD16" s="2" t="n">
+      <c r="CH16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI16" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5154,7 +5184,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -5397,16 +5427,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA17" s="3" t="n">
+      <c r="CF17" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB17" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC17" s="3" t="n">
+      <c r="CG17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH17" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD17" s="3" t="n">
+      <c r="CI17" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5432,7 +5462,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -5675,16 +5705,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD18" s="2" t="n">
+      <c r="CF18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI18" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5710,7 +5740,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -5953,16 +5983,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA19" s="3" t="n">
+      <c r="CF19" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB19" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC19" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD19" s="3" t="n">
+      <c r="CG19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI19" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5988,7 +6018,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -6231,16 +6261,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA20" s="2" t="n">
+      <c r="CF20" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB20" s="2" t="n">
+      <c r="CG20" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC20" s="2" t="n">
+      <c r="CH20" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD20" s="2" t="n">
+      <c r="CI20" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6266,7 +6296,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -6509,16 +6539,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA21" s="3" t="n">
+      <c r="CF21" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB21" s="3" t="n">
+      <c r="CG21" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC21" s="3" t="n">
+      <c r="CH21" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD21" s="3" t="n">
+      <c r="CI21" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6544,7 +6574,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -6787,16 +6817,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA22" s="2" t="n">
+      <c r="CF22" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC22" s="2" t="n">
+      <c r="CG22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH22" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD22" s="2" t="n">
+      <c r="CI22" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6822,7 +6852,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -7065,16 +7095,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA23" s="3" t="n">
+      <c r="CF23" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB23" s="3" t="n">
+      <c r="CG23" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC23" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD23" s="3" t="n">
+      <c r="CH23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI23" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7343,16 +7373,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB24" s="2" t="n">
+      <c r="CF24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG24" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC24" s="2" t="n">
+      <c r="CH24" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD24" s="2" t="n">
+      <c r="CI24" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7378,7 +7408,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -7621,16 +7651,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA25" s="3" t="n">
+      <c r="CF25" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB25" s="3" t="n">
+      <c r="CG25" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC25" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD25" s="3" t="n">
+      <c r="CH25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI25" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7899,16 +7929,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA26" s="2" t="n">
+      <c r="CF26" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CB26" s="2" t="n">
+      <c r="CG26" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC26" s="2" t="n">
+      <c r="CH26" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD26" s="2" t="n">
+      <c r="CI26" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7934,7 +7964,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -8177,16 +8207,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA27" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB27" s="3" t="n">
+      <c r="CF27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG27" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC27" s="3" t="n">
+      <c r="CH27" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD27" s="3" t="n">
+      <c r="CI27" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8212,7 +8242,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -8455,16 +8485,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA28" s="2" t="n">
+      <c r="CF28" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB28" s="2" t="n">
+      <c r="CG28" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC28" s="2" t="n">
+      <c r="CH28" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD28" s="2" t="n">
+      <c r="CI28" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8490,7 +8520,7 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -8733,16 +8763,16 @@
           <t>Show to senior officer for decision</t>
         </is>
       </c>
-      <c r="CA29" s="3" t="n">
+      <c r="CF29" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB29" s="3" t="n">
+      <c r="CG29" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC29" s="3" t="n">
+      <c r="CH29" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD29" s="3" t="n">
+      <c r="CI29" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8768,7 +8798,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -9011,16 +9041,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA30" s="2" t="n">
+      <c r="CF30" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB30" s="2" t="n">
+      <c r="CG30" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD30" s="2" t="n">
+      <c r="CH30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI30" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9046,7 +9076,7 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -9289,16 +9319,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA31" s="3" t="n">
+      <c r="CF31" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="CB31" s="3" t="n">
+      <c r="CG31" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC31" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD31" s="3" t="n">
+      <c r="CH31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI31" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9324,7 +9354,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -9567,16 +9597,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC32" s="2" t="n">
+      <c r="CF32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH32" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD32" s="2" t="n">
+      <c r="CI32" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9602,7 +9632,7 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -9845,16 +9875,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB33" s="3" t="n">
+      <c r="CF33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG33" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD33" s="3" t="n">
+      <c r="CH33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI33" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9880,7 +9910,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -10123,16 +10153,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA34" s="2" t="n">
+      <c r="CF34" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB34" s="2" t="n">
+      <c r="CG34" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC34" s="2" t="n">
+      <c r="CH34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="CD34" s="2" t="n">
+      <c r="CI34" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10158,7 +10188,7 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -10401,16 +10431,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA35" s="3" t="n">
+      <c r="CF35" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB35" s="3" t="n">
+      <c r="CG35" s="3" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC35" s="3" t="n">
+      <c r="CH35" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD35" s="3" t="n">
+      <c r="CI35" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10436,7 +10466,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -10679,16 +10709,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA36" s="2" t="n">
+      <c r="CF36" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB36" s="2" t="n">
+      <c r="CG36" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC36" s="2" t="n">
+      <c r="CH36" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD36" s="2" t="n">
+      <c r="CI36" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10957,16 +10987,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA37" s="3" t="n">
+      <c r="CF37" s="3" t="n">
         <v>4.75</v>
       </c>
-      <c r="CB37" s="3" t="n">
+      <c r="CG37" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC37" s="3" t="n">
+      <c r="CH37" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="CD37" s="3" t="n">
+      <c r="CI37" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10992,7 +11022,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -11235,16 +11265,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA38" s="2" t="n">
+      <c r="CF38" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB38" s="2" t="n">
+      <c r="CG38" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC38" s="2" t="n">
+      <c r="CH38" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD38" s="2" t="n">
+      <c r="CI38" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11270,7 +11300,7 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -11513,16 +11543,16 @@
           <t>Show to senior officer for decision</t>
         </is>
       </c>
-      <c r="CA39" s="3" t="n">
+      <c r="CF39" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB39" s="3" t="n">
+      <c r="CG39" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC39" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD39" s="3" t="n">
+      <c r="CH39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI39" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11548,7 +11578,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -11791,16 +11821,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA40" s="2" t="n">
+      <c r="CF40" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB40" s="2" t="n">
+      <c r="CG40" s="2" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC40" s="2" t="n">
+      <c r="CH40" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD40" s="2" t="n">
+      <c r="CI40" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11826,7 +11856,7 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -12069,16 +12099,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA41" s="3" t="n">
+      <c r="CF41" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB41" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC41" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD41" s="3" t="n">
+      <c r="CG41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI41" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12347,16 +12377,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA42" s="2" t="n">
+      <c r="CF42" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB42" s="2" t="n">
+      <c r="CG42" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC42" s="2" t="n">
+      <c r="CH42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="CD42" s="2" t="n">
+      <c r="CI42" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -12382,7 +12412,7 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -12625,16 +12655,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA43" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB43" s="3" t="n">
+      <c r="CF43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG43" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD43" s="3" t="n">
+      <c r="CH43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI43" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12660,7 +12690,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -12903,16 +12933,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD44" s="2" t="n">
+      <c r="CF44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI44" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12938,7 +12968,7 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -13181,16 +13211,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA45" s="3" t="n">
+      <c r="CF45" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB45" s="3" t="n">
+      <c r="CG45" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC45" s="3" t="n">
+      <c r="CH45" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD45" s="3" t="n">
+      <c r="CI45" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13216,7 +13246,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -13459,16 +13489,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA46" s="2" t="n">
+      <c r="CF46" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB46" s="2" t="n">
+      <c r="CG46" s="2" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD46" s="2" t="n">
+      <c r="CH46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI46" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13494,7 +13524,7 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -13737,16 +13767,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA47" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB47" s="3" t="n">
+      <c r="CF47" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG47" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC47" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD47" s="3" t="n">
+      <c r="CH47" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI47" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14015,16 +14045,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA48" s="2" t="n">
+      <c r="CF48" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="CB48" s="2" t="n">
+      <c r="CG48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="CC48" s="2" t="n">
+      <c r="CH48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="CD48" s="2" t="n">
+      <c r="CI48" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14050,7 +14080,7 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -14293,16 +14323,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA49" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB49" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC49" s="3" t="n">
+      <c r="CF49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH49" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD49" s="3" t="n">
+      <c r="CI49" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14328,7 +14358,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -14571,16 +14601,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA50" s="2" t="n">
+      <c r="CF50" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB50" s="2" t="n">
+      <c r="CG50" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC50" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD50" s="2" t="n">
+      <c r="CH50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI50" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14606,7 +14636,7 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -14849,16 +14879,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA51" s="3" t="n">
+      <c r="CF51" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB51" s="3" t="n">
+      <c r="CG51" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC51" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD51" s="3" t="n">
+      <c r="CH51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI51" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14884,7 +14914,7 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -15127,16 +15157,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA52" s="2" t="n">
+      <c r="CF52" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD52" s="2" t="n">
+      <c r="CG52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI52" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15162,7 +15192,7 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -15405,16 +15435,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA53" s="3" t="n">
+      <c r="CF53" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB53" s="3" t="n">
+      <c r="CG53" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC53" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD53" s="3" t="n">
+      <c r="CH53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI53" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15683,16 +15713,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA54" s="2" t="n">
+      <c r="CF54" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="CB54" s="2" t="n">
+      <c r="CG54" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC54" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD54" s="2" t="n">
+      <c r="CH54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI54" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -15718,7 +15748,7 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -15961,16 +15991,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA55" s="3" t="n">
+      <c r="CF55" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB55" s="3" t="n">
+      <c r="CG55" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC55" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD55" s="3" t="n">
+      <c r="CH55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI55" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15996,7 +16026,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -16239,16 +16269,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA56" s="2" t="n">
+      <c r="CF56" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB56" s="2" t="n">
+      <c r="CG56" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC56" s="2" t="n">
+      <c r="CH56" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD56" s="2" t="n">
+      <c r="CI56" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -16274,7 +16304,7 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -16517,16 +16547,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA57" s="3" t="n">
+      <c r="CF57" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB57" s="3" t="n">
+      <c r="CG57" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC57" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD57" s="3" t="n">
+      <c r="CH57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI57" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -16552,7 +16582,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -16795,16 +16825,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA58" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB58" s="2" t="n">
+      <c r="CF58" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG58" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD58" s="2" t="n">
+      <c r="CH58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI58" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -16830,7 +16860,7 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -17073,16 +17103,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA59" s="3" t="n">
+      <c r="CF59" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB59" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC59" s="3" t="n">
+      <c r="CG59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH59" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD59" s="3" t="n">
+      <c r="CI59" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -17108,7 +17138,7 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -17351,16 +17381,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA60" s="2" t="n">
+      <c r="CF60" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC60" s="2" t="n">
+      <c r="CG60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH60" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD60" s="2" t="n">
+      <c r="CI60" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -17386,7 +17416,7 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -17629,16 +17659,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA61" s="3" t="n">
+      <c r="CF61" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB61" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC61" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD61" s="3" t="n">
+      <c r="CG61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI61" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -17664,7 +17694,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -17907,16 +17937,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA62" s="2" t="n">
+      <c r="CF62" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD62" s="2" t="n">
+      <c r="CG62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI62" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17942,7 +17972,7 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -18185,16 +18215,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA63" s="3" t="n">
+      <c r="CF63" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB63" s="3" t="n">
+      <c r="CG63" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC63" s="3" t="n">
+      <c r="CH63" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD63" s="3" t="n">
+      <c r="CI63" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18220,7 +18250,7 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -18463,16 +18493,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA64" s="2" t="n">
+      <c r="CF64" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB64" s="2" t="n">
+      <c r="CG64" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC64" s="2" t="n">
+      <c r="CH64" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD64" s="2" t="n">
+      <c r="CI64" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -18498,7 +18528,7 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -18741,16 +18771,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA65" s="3" t="n">
+      <c r="CF65" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB65" s="3" t="n">
+      <c r="CG65" s="3" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC65" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD65" s="3" t="n">
+      <c r="CH65" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI65" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -18776,7 +18806,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -19019,16 +19049,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA66" s="2" t="n">
+      <c r="CF66" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB66" s="2" t="n">
+      <c r="CG66" s="2" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD66" s="2" t="n">
+      <c r="CH66" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI66" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -19054,7 +19084,7 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -19297,16 +19327,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA67" s="3" t="n">
+      <c r="CF67" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB67" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC67" s="3" t="n">
+      <c r="CG67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH67" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD67" s="3" t="n">
+      <c r="CI67" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -19332,7 +19362,7 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -19575,16 +19605,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA68" s="2" t="n">
+      <c r="CF68" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB68" s="2" t="n">
+      <c r="CG68" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC68" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD68" s="2" t="n">
+      <c r="CH68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI68" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -19610,7 +19640,7 @@
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -19853,16 +19883,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA69" s="3" t="n">
+      <c r="CF69" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB69" s="3" t="n">
+      <c r="CG69" s="3" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC69" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD69" s="3" t="n">
+      <c r="CH69" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI69" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -19888,7 +19918,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -20131,16 +20161,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA70" s="2" t="n">
+      <c r="CF70" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB70" s="2" t="n">
+      <c r="CG70" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC70" s="2" t="n">
+      <c r="CH70" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="CD70" s="2" t="n">
+      <c r="CI70" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -20409,16 +20439,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA71" s="3" t="n">
+      <c r="CF71" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="CB71" s="3" t="n">
+      <c r="CG71" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="CC71" s="3" t="n">
+      <c r="CH71" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD71" s="3" t="n">
+      <c r="CI71" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -20444,7 +20474,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -20687,16 +20717,16 @@
           <t>Show to senior officer for decision</t>
         </is>
       </c>
-      <c r="CA72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB72" s="2" t="n">
+      <c r="CF72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG72" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD72" s="2" t="n">
+      <c r="CH72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI72" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -20722,7 +20752,7 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -20965,16 +20995,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA73" s="3" t="n">
+      <c r="CF73" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB73" s="3" t="n">
+      <c r="CG73" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC73" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD73" s="3" t="n">
+      <c r="CH73" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI73" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -21000,7 +21030,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -21243,16 +21273,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD74" s="2" t="n">
+      <c r="CF74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI74" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21278,7 +21308,7 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -21521,16 +21551,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA75" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB75" s="3" t="n">
+      <c r="CF75" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG75" s="3" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC75" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD75" s="3" t="n">
+      <c r="CH75" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI75" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -21556,7 +21586,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -21799,16 +21829,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA76" s="2" t="n">
+      <c r="CF76" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="CB76" s="2" t="n">
+      <c r="CG76" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC76" s="2" t="n">
+      <c r="CH76" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD76" s="2" t="n">
+      <c r="CI76" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -21834,7 +21864,7 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -22077,16 +22107,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA77" s="3" t="n">
+      <c r="CF77" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB77" s="3" t="n">
+      <c r="CG77" s="3" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC77" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD77" s="3" t="n">
+      <c r="CH77" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI77" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22355,16 +22385,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA78" s="2" t="n">
+      <c r="CF78" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="CB78" s="2" t="n">
+      <c r="CG78" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC78" s="2" t="n">
+      <c r="CH78" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD78" s="2" t="n">
+      <c r="CI78" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22390,7 +22420,7 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -22633,16 +22663,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA79" s="3" t="n">
+      <c r="CF79" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB79" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC79" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD79" s="3" t="n">
+      <c r="CG79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI79" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22668,7 +22698,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -22911,16 +22941,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA80" s="2" t="n">
+      <c r="CF80" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB80" s="2" t="n">
+      <c r="CG80" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD80" s="2" t="n">
+      <c r="CH80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI80" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -22946,7 +22976,7 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -23189,16 +23219,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA81" s="3" t="n">
+      <c r="CF81" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB81" s="3" t="n">
+      <c r="CG81" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC81" s="3" t="n">
+      <c r="CH81" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD81" s="3" t="n">
+      <c r="CI81" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23224,7 +23254,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -23475,16 +23505,16 @@
           <t>Wait and retry after some time</t>
         </is>
       </c>
-      <c r="CA82" s="2" t="n">
+      <c r="CF82" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="CB82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC82" s="2" t="n">
+      <c r="CG82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH82" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD82" s="2" t="n">
+      <c r="CI82" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23510,7 +23540,7 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -23761,16 +23791,16 @@
           <t>Switch to manual register and upload later</t>
         </is>
       </c>
-      <c r="CA83" s="3" t="n">
+      <c r="CF83" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB83" s="3" t="n">
+      <c r="CG83" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC83" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD83" s="3" t="n">
+      <c r="CH83" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI83" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -23796,7 +23826,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -24047,16 +24077,16 @@
           <t>Call block office for help</t>
         </is>
       </c>
-      <c r="CA84" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC84" s="2" t="n">
+      <c r="CF84" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH84" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD84" s="2" t="n">
+      <c r="CI84" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -24082,7 +24112,7 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -24333,16 +24363,16 @@
           <t>Skip the task for the day</t>
         </is>
       </c>
-      <c r="CA85" s="3" t="n">
+      <c r="CF85" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB85" s="3" t="n">
+      <c r="CG85" s="3" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC85" s="3" t="n">
+      <c r="CH85" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD85" s="3" t="n">
+      <c r="CI85" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -24368,7 +24398,7 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -24619,16 +24649,16 @@
           <t>Use mobile data and try again</t>
         </is>
       </c>
-      <c r="CA86" s="2" t="n">
+      <c r="CF86" s="2" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB86" s="2" t="n">
+      <c r="CG86" s="2" t="n">
         <v>2.33</v>
       </c>
-      <c r="CC86" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD86" s="2" t="n">
+      <c r="CH86" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI86" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -24654,7 +24684,7 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -24905,16 +24935,16 @@
           <t>Switch to manual register and upload later</t>
         </is>
       </c>
-      <c r="CA87" s="3" t="n">
+      <c r="CF87" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB87" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC87" s="3" t="n">
+      <c r="CG87" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH87" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD87" s="3" t="n">
+      <c r="CI87" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -24940,7 +24970,7 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -25191,16 +25221,16 @@
           <t>Switch to manual register and upload later</t>
         </is>
       </c>
-      <c r="CA88" s="2" t="n">
+      <c r="CF88" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="CB88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC88" s="2" t="n">
+      <c r="CG88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH88" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD88" s="2" t="n">
+      <c r="CI88" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25226,7 +25256,7 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -25477,16 +25507,16 @@
           <t>Switch to manual register and upload later</t>
         </is>
       </c>
-      <c r="CA89" s="3" t="n">
+      <c r="CF89" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB89" s="3" t="n">
+      <c r="CG89" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC89" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD89" s="3" t="n">
+      <c r="CH89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI89" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -25512,7 +25542,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -25763,16 +25793,16 @@
           <t>Skip the task for the day</t>
         </is>
       </c>
-      <c r="CA90" s="2" t="n">
+      <c r="CF90" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB90" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC90" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD90" s="2" t="n">
+      <c r="CG90" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH90" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI90" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -25798,7 +25828,7 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
@@ -26049,16 +26079,16 @@
           <t>Wait and retry after some time</t>
         </is>
       </c>
-      <c r="CA91" s="3" t="n">
+      <c r="CF91" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB91" s="3" t="n">
+      <c r="CG91" s="3" t="n">
         <v>2.33</v>
       </c>
-      <c r="CC91" s="3" t="n">
+      <c r="CH91" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD91" s="3" t="n">
+      <c r="CI91" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -26084,7 +26114,7 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -26335,16 +26365,16 @@
           <t>Wait and retry after some time</t>
         </is>
       </c>
-      <c r="CA92" s="2" t="n">
+      <c r="CF92" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CB92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD92" s="2" t="n">
+      <c r="CG92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI92" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26370,7 +26400,7 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -26621,16 +26651,16 @@
           <t>Call block office for help</t>
         </is>
       </c>
-      <c r="CA93" s="3" t="n">
+      <c r="CF93" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB93" s="3" t="n">
+      <c r="CG93" s="3" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC93" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD93" s="3" t="n">
+      <c r="CH93" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI93" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -26656,7 +26686,7 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -26907,16 +26937,16 @@
           <t>Use mobile data and try again</t>
         </is>
       </c>
-      <c r="CA94" s="2" t="n">
+      <c r="CF94" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB94" s="2" t="n">
+      <c r="CG94" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC94" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD94" s="2" t="n">
+      <c r="CH94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI94" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -26942,7 +26972,7 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -27193,16 +27223,16 @@
           <t>Call block office for help</t>
         </is>
       </c>
-      <c r="CA95" s="3" t="n">
+      <c r="CF95" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CB95" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC95" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD95" s="3" t="n">
+      <c r="CG95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH95" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI95" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -27228,7 +27258,7 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -27479,16 +27509,16 @@
           <t>Call block office for help</t>
         </is>
       </c>
-      <c r="CA96" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB96" s="2" t="n">
+      <c r="CF96" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG96" s="2" t="n">
         <v>2.33</v>
       </c>
-      <c r="CC96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD96" s="2" t="n">
+      <c r="CH96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI96" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -27514,7 +27544,7 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -27765,16 +27795,16 @@
           <t>Switch to manual register and upload later</t>
         </is>
       </c>
-      <c r="CA97" s="3" t="n">
+      <c r="CF97" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="CB97" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC97" s="3" t="n">
+      <c r="CG97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH97" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD97" s="3" t="n">
+      <c r="CI97" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27800,7 +27830,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -28051,16 +28081,16 @@
           <t>Call block office for help</t>
         </is>
       </c>
-      <c r="CA98" s="2" t="n">
+      <c r="CF98" s="2" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD98" s="2" t="n">
+      <c r="CG98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI98" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -28086,7 +28116,7 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -28337,16 +28367,16 @@
           <t>Use mobile data and try again</t>
         </is>
       </c>
-      <c r="CA99" s="3" t="n">
+      <c r="CF99" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB99" s="3" t="n">
+      <c r="CG99" s="3" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC99" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD99" s="3" t="n">
+      <c r="CH99" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI99" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -28623,16 +28653,16 @@
           <t>Switch to manual register and upload later</t>
         </is>
       </c>
-      <c r="CA100" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB100" s="2" t="n">
+      <c r="CF100" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG100" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC100" s="2" t="n">
+      <c r="CH100" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD100" s="2" t="n">
+      <c r="CI100" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -28658,7 +28688,7 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -28909,16 +28939,16 @@
           <t>Skip the task for the day</t>
         </is>
       </c>
-      <c r="CA101" s="3" t="n">
+      <c r="CF101" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB101" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC101" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD101" s="3" t="n">
+      <c r="CG101" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH101" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI101" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29195,16 +29225,16 @@
           <t>Use mobile data and try again</t>
         </is>
       </c>
-      <c r="CA102" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB102" s="2" t="n">
+      <c r="CF102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG102" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC102" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD102" s="2" t="n">
+      <c r="CH102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI102" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -29230,7 +29260,7 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -29481,16 +29511,16 @@
           <t>Switch to manual register and upload later</t>
         </is>
       </c>
-      <c r="CA103" s="3" t="n">
+      <c r="CF103" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB103" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC103" s="3" t="n">
+      <c r="CG103" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH103" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD103" s="3" t="n">
+      <c r="CI103" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29516,7 +29546,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -29767,16 +29797,16 @@
           <t>Use mobile data and try again</t>
         </is>
       </c>
-      <c r="CA104" s="2" t="n">
+      <c r="CF104" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB104" s="2" t="n">
+      <c r="CG104" s="2" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC104" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD104" s="2" t="n">
+      <c r="CH104" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI104" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -29802,7 +29832,7 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -30053,16 +30083,16 @@
           <t>Use mobile data and try again</t>
         </is>
       </c>
-      <c r="CA105" s="3" t="n">
+      <c r="CF105" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="CB105" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC105" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD105" s="3" t="n">
+      <c r="CG105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI105" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30088,7 +30118,7 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -30339,16 +30369,16 @@
           <t>Use mobile data and try again</t>
         </is>
       </c>
-      <c r="CA106" s="2" t="n">
+      <c r="CF106" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="CB106" s="2" t="n">
+      <c r="CG106" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD106" s="2" t="n">
+      <c r="CH106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI106" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30374,7 +30404,7 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -30625,16 +30655,16 @@
           <t>Call block office for help</t>
         </is>
       </c>
-      <c r="CA107" s="3" t="n">
+      <c r="CF107" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB107" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC107" s="3" t="n">
+      <c r="CG107" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH107" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD107" s="3" t="n">
+      <c r="CI107" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -30660,7 +30690,7 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -30911,16 +30941,16 @@
           <t>Wait and retry after some time</t>
         </is>
       </c>
-      <c r="CA108" s="2" t="n">
+      <c r="CF108" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CB108" s="2" t="n">
+      <c r="CG108" s="2" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD108" s="2" t="n">
+      <c r="CH108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI108" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31197,16 +31227,16 @@
           <t>Contact NIC helpdesk</t>
         </is>
       </c>
-      <c r="CA109" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB109" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC109" s="3" t="n">
+      <c r="CF109" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG109" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH109" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD109" s="3" t="n">
+      <c r="CI109" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -31232,7 +31262,7 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -31483,16 +31513,16 @@
           <t>Use mobile data and try again</t>
         </is>
       </c>
-      <c r="CA110" s="2" t="n">
+      <c r="CF110" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB110" s="2" t="n">
+      <c r="CG110" s="2" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD110" s="2" t="n">
+      <c r="CH110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI110" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31518,7 +31548,7 @@
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -31769,16 +31799,16 @@
           <t>Switch to manual register and upload later</t>
         </is>
       </c>
-      <c r="CA111" s="3" t="n">
+      <c r="CF111" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB111" s="3" t="n">
+      <c r="CG111" s="3" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC111" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD111" s="3" t="n">
+      <c r="CH111" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI111" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31804,7 +31834,7 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -32055,16 +32085,16 @@
           <t>Use mobile data and try again</t>
         </is>
       </c>
-      <c r="CA112" s="2" t="n">
+      <c r="CF112" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB112" s="2" t="n">
+      <c r="CG112" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC112" s="2" t="n">
+      <c r="CH112" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD112" s="2" t="n">
+      <c r="CI112" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32090,7 +32120,7 @@
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -32341,16 +32371,16 @@
           <t>Call block office for help</t>
         </is>
       </c>
-      <c r="CA113" s="3" t="n">
+      <c r="CF113" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB113" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC113" s="3" t="n">
+      <c r="CG113" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH113" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD113" s="3" t="n">
+      <c r="CI113" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -32376,7 +32406,7 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -32627,16 +32657,16 @@
           <t>Use mobile data and try again</t>
         </is>
       </c>
-      <c r="CA114" s="2" t="n">
+      <c r="CF114" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB114" s="2" t="n">
+      <c r="CG114" s="2" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD114" s="2" t="n">
+      <c r="CH114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI114" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -32662,7 +32692,7 @@
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -32913,16 +32943,16 @@
           <t>Switch to manual register and upload later</t>
         </is>
       </c>
-      <c r="CA115" s="3" t="n">
+      <c r="CF115" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB115" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC115" s="3" t="n">
+      <c r="CG115" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH115" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD115" s="3" t="n">
+      <c r="CI115" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -32948,7 +32978,7 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -33199,16 +33229,16 @@
           <t>Wait and retry after some time</t>
         </is>
       </c>
-      <c r="CA116" s="2" t="n">
+      <c r="CF116" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB116" s="2" t="n">
+      <c r="CG116" s="2" t="n">
         <v>2.33</v>
       </c>
-      <c r="CC116" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD116" s="2" t="n">
+      <c r="CH116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI116" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -33234,7 +33264,7 @@
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -33485,16 +33515,16 @@
           <t>Switch to manual register and upload later</t>
         </is>
       </c>
-      <c r="CA117" s="3" t="n">
+      <c r="CF117" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB117" s="3" t="n">
+      <c r="CG117" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC117" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD117" s="3" t="n">
+      <c r="CH117" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI117" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -33520,7 +33550,7 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -33771,16 +33801,16 @@
           <t>Call block office for help</t>
         </is>
       </c>
-      <c r="CA118" s="2" t="n">
+      <c r="CF118" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB118" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC118" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD118" s="2" t="n">
+      <c r="CG118" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH118" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI118" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -33806,7 +33836,7 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -34057,16 +34087,16 @@
           <t>Wait and retry after some time</t>
         </is>
       </c>
-      <c r="CA119" s="3" t="n">
+      <c r="CF119" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB119" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC119" s="3" t="n">
+      <c r="CG119" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH119" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD119" s="3" t="n">
+      <c r="CI119" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -34092,7 +34122,7 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -34343,16 +34373,16 @@
           <t>Skip the task for the day</t>
         </is>
       </c>
-      <c r="CA120" s="2" t="n">
+      <c r="CF120" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="CB120" s="2" t="n">
+      <c r="CG120" s="2" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC120" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD120" s="2" t="n">
+      <c r="CH120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI120" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -34378,7 +34408,7 @@
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -34629,16 +34659,16 @@
           <t>Call block office for help</t>
         </is>
       </c>
-      <c r="CA121" s="3" t="n">
+      <c r="CF121" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB121" s="3" t="n">
+      <c r="CG121" s="3" t="n">
         <v>2.33</v>
       </c>
-      <c r="CC121" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD121" s="3" t="n">
+      <c r="CH121" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI121" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -34664,7 +34694,7 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -34913,16 +34943,16 @@
       <c r="BN122" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="CA122" s="2" t="n">
+      <c r="CF122" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB122" s="2" t="n">
+      <c r="CG122" s="2" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC122" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD122" s="2" t="n">
+      <c r="CH122" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI122" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -34948,7 +34978,7 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
@@ -35197,16 +35227,16 @@
       <c r="BN123" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="CA123" s="3" t="n">
+      <c r="CF123" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB123" s="3" t="n">
+      <c r="CG123" s="3" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC123" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD123" s="3" t="n">
+      <c r="CH123" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI123" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -35232,7 +35262,7 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -35481,16 +35511,16 @@
       <c r="BN124" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="CA124" s="2" t="n">
+      <c r="CF124" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB124" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC124" s="2" t="n">
+      <c r="CG124" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH124" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD124" s="2" t="n">
+      <c r="CI124" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -35516,7 +35546,7 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
@@ -35765,16 +35795,16 @@
       <c r="BN125" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="CA125" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB125" s="3" t="n">
+      <c r="CF125" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG125" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC125" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD125" s="3" t="n">
+      <c r="CH125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI125" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -35800,7 +35830,7 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -36049,16 +36079,16 @@
       <c r="BN126" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="CA126" s="2" t="n">
+      <c r="CF126" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB126" s="2" t="n">
+      <c r="CG126" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC126" s="2" t="n">
+      <c r="CH126" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD126" s="2" t="n">
+      <c r="CI126" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -36333,16 +36363,16 @@
       <c r="BN127" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="CA127" s="3" t="n">
+      <c r="CF127" s="3" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB127" s="3" t="n">
+      <c r="CG127" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC127" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD127" s="3" t="n">
+      <c r="CH127" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI127" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -36368,7 +36398,7 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -36617,16 +36647,16 @@
       <c r="BN128" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="CA128" s="2" t="n">
+      <c r="CF128" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CB128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD128" s="2" t="n">
+      <c r="CG128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI128" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -36652,7 +36682,7 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
@@ -36901,16 +36931,16 @@
       <c r="BN129" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="CA129" s="3" t="n">
+      <c r="CF129" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB129" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC129" s="3" t="n">
+      <c r="CG129" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH129" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD129" s="3" t="n">
+      <c r="CI129" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -36936,7 +36966,7 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -37185,16 +37215,16 @@
       <c r="BN130" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="CA130" s="2" t="n">
+      <c r="CF130" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB130" s="2" t="n">
+      <c r="CG130" s="2" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC130" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD130" s="2" t="n">
+      <c r="CH130" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI130" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -37220,7 +37250,7 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -37469,16 +37499,16 @@
       <c r="BN131" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="CA131" s="3" t="n">
+      <c r="CF131" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB131" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC131" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD131" s="3" t="n">
+      <c r="CG131" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH131" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI131" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -37753,16 +37783,16 @@
       <c r="BN132" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="CA132" s="2" t="n">
+      <c r="CF132" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CB132" s="2" t="n">
+      <c r="CG132" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="CC132" s="2" t="n">
+      <c r="CH132" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD132" s="2" t="n">
+      <c r="CI132" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -37788,7 +37818,7 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -38037,16 +38067,16 @@
       <c r="BN133" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="CA133" s="3" t="n">
+      <c r="CF133" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB133" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC133" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD133" s="3" t="n">
+      <c r="CG133" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH133" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI133" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -38072,7 +38102,7 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -38321,16 +38351,16 @@
       <c r="BN134" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="CA134" s="2" t="n">
+      <c r="CF134" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB134" s="2" t="n">
+      <c r="CG134" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC134" s="2" t="n">
+      <c r="CH134" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD134" s="2" t="n">
+      <c r="CI134" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -38356,7 +38386,7 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -38605,16 +38635,16 @@
       <c r="BN135" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="CA135" s="3" t="n">
+      <c r="CF135" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="CB135" s="3" t="n">
+      <c r="CG135" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC135" s="3" t="n">
+      <c r="CH135" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD135" s="3" t="n">
+      <c r="CI135" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -38640,7 +38670,7 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -38889,16 +38919,16 @@
       <c r="BN136" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="CA136" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB136" s="2" t="n">
+      <c r="CF136" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG136" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC136" s="2" t="n">
+      <c r="CH136" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD136" s="2" t="n">
+      <c r="CI136" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -38924,7 +38954,7 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
@@ -39173,16 +39203,16 @@
       <c r="BN137" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="CA137" s="3" t="n">
+      <c r="CF137" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="CB137" s="3" t="n">
+      <c r="CG137" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC137" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD137" s="3" t="n">
+      <c r="CH137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI137" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -39208,7 +39238,7 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -39457,16 +39487,16 @@
       <c r="BN138" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="CA138" s="2" t="n">
+      <c r="CF138" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB138" s="2" t="n">
+      <c r="CG138" s="2" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC138" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD138" s="2" t="n">
+      <c r="CH138" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI138" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -39492,7 +39522,7 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -39741,16 +39771,16 @@
       <c r="BN139" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="CA139" s="3" t="n">
+      <c r="CF139" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB139" s="3" t="n">
+      <c r="CG139" s="3" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC139" s="3" t="n">
+      <c r="CH139" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD139" s="3" t="n">
+      <c r="CI139" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -39776,7 +39806,7 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -40025,16 +40055,16 @@
       <c r="BN140" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="CA140" s="2" t="n">
+      <c r="CF140" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB140" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC140" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD140" s="2" t="n">
+      <c r="CG140" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH140" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI140" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -40060,7 +40090,7 @@
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -40309,21 +40339,3783 @@
       <c r="BN141" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="CA141" s="3" t="n">
+      <c r="CF141" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB141" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC141" s="3" t="n">
+      <c r="CG141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH141" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD141" s="3" t="n">
+      <c r="CI141" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>R141</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Upper Collector / Class I</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>46-60</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>21+</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>Strongly agree</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" s="2" t="inlineStr">
+        <is>
+          <t>desktop, laptop, phone</t>
+        </is>
+      </c>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y142" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="Z142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA142" s="2" t="inlineStr">
+        <is>
+          <t>Same day</t>
+        </is>
+      </c>
+      <c r="AB142" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AC142" s="2" t="inlineStr">
+        <is>
+          <t>81-100%</t>
+        </is>
+      </c>
+      <c r="AD142" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1 day</t>
+        </is>
+      </c>
+      <c r="AE142" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF142" s="2" t="inlineStr">
+        <is>
+          <t>e-Office, email, MS Office</t>
+        </is>
+      </c>
+      <c r="AG142" s="2" t="inlineStr">
+        <is>
+          <t>Review/approve</t>
+        </is>
+      </c>
+      <c r="AH142" s="2" t="inlineStr">
+        <is>
+          <t>Everyone does own</t>
+        </is>
+      </c>
+      <c r="AI142" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AJ142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK142" s="2" t="inlineStr">
+        <is>
+          <t>Fix myself</t>
+        </is>
+      </c>
+      <c r="AL142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM142" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp, Google Drive</t>
+        </is>
+      </c>
+      <c r="AN142" s="2" t="inlineStr">
+        <is>
+          <t>Coordinating, sharing files</t>
+        </is>
+      </c>
+      <c r="AO142" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ142" s="2" t="inlineStr">
+        <is>
+          <t>Need official communication platform to replace WhatsApp for sensitive data</t>
+        </is>
+      </c>
+      <c r="AR142" s="2" t="inlineStr">
+        <is>
+          <t>Slow internet, Portal crashes</t>
+        </is>
+      </c>
+      <c r="AS142" s="2" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="AT142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV142" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW142" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX142" s="2" t="inlineStr">
+        <is>
+          <t>e-Office</t>
+        </is>
+      </c>
+      <c r="AY142" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA142" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD142" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE142" s="2" t="inlineStr">
+        <is>
+          <t>1.Internet 2.Training 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF142" s="2" t="inlineStr">
+        <is>
+          <t>Stable internet connectivity</t>
+        </is>
+      </c>
+      <c r="BG142" s="2" t="inlineStr">
+        <is>
+          <t>Yes significantly</t>
+        </is>
+      </c>
+      <c r="BH142" s="2" t="inlineStr">
+        <is>
+          <t>MP Bhulekh, RCMS, SAMPADA 2.0</t>
+        </is>
+      </c>
+      <c r="BI142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ142" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK142" s="2" t="inlineStr">
+        <is>
+          <t>21-40%</t>
+        </is>
+      </c>
+      <c r="BL142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM142" s="2" t="inlineStr">
+        <is>
+          <t>Online mutation is faster</t>
+        </is>
+      </c>
+      <c r="BN142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CF142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG142" s="2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="CH142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI142" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>R142</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>AG 3 / Class III</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>6-10</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>Agree somewhat</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N143" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O143" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S143" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V143" s="3" t="inlineStr">
+        <is>
+          <t>desktop, phone</t>
+        </is>
+      </c>
+      <c r="W143" s="3" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="X143" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y143" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="Z143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA143" s="3" t="inlineStr">
+        <is>
+          <t>2-3 days</t>
+        </is>
+      </c>
+      <c r="AB143" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AC143" s="3" t="inlineStr">
+        <is>
+          <t>81-100%</t>
+        </is>
+      </c>
+      <c r="AD143" s="3" t="inlineStr">
+        <is>
+          <t>1-2 weeks</t>
+        </is>
+      </c>
+      <c r="AE143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF143" s="3" t="inlineStr">
+        <is>
+          <t>e-Office, PFMS</t>
+        </is>
+      </c>
+      <c r="AG143" s="3" t="inlineStr">
+        <is>
+          <t>Data entry</t>
+        </is>
+      </c>
+      <c r="AH143" s="3" t="inlineStr">
+        <is>
+          <t>A few share</t>
+        </is>
+      </c>
+      <c r="AI143" s="3" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AJ143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK143" s="3" t="inlineStr">
+        <is>
+          <t>Ask colleague</t>
+        </is>
+      </c>
+      <c r="AL143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM143" s="3" t="inlineStr">
+        <is>
+          <t>WhatsApp, Google Docs</t>
+        </is>
+      </c>
+      <c r="AN143" s="3" t="inlineStr">
+        <is>
+          <t>Communication, drafting</t>
+        </is>
+      </c>
+      <c r="AO143" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ143" s="3" t="inlineStr">
+        <is>
+          <t>Data security concerns with personal devices</t>
+        </is>
+      </c>
+      <c r="AR143" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet, Old computers</t>
+        </is>
+      </c>
+      <c r="AS143" s="3" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="AT143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU143" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV143" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW143" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX143" s="3" t="inlineStr">
+        <is>
+          <t>basic computer operations</t>
+        </is>
+      </c>
+      <c r="AY143" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA143" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD143" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE143" s="3" t="inlineStr">
+        <is>
+          <t>1.Training 2.Internet 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF143" s="3" t="inlineStr">
+        <is>
+          <t>Simplified Hindi interface</t>
+        </is>
+      </c>
+      <c r="BG143" s="3" t="inlineStr">
+        <is>
+          <t>Yes significantly</t>
+        </is>
+      </c>
+      <c r="BH143" s="3" t="inlineStr">
+        <is>
+          <t>MP Bhulekh, RCMS</t>
+        </is>
+      </c>
+      <c r="BI143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK143" s="3" t="inlineStr">
+        <is>
+          <t>41-60%</t>
+        </is>
+      </c>
+      <c r="BL143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM143" s="3" t="inlineStr">
+        <is>
+          <t>Mutation backlog exists due to server errors</t>
+        </is>
+      </c>
+      <c r="BN143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF143" s="3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="CG143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH143" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CI143" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>R143</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>AG 3 / Class III</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>11-20</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Grad</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>Agree somewhat</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V144" s="2" t="inlineStr">
+        <is>
+          <t>desktop, phone</t>
+        </is>
+      </c>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="X144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y144" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="Z144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA144" s="2" t="inlineStr">
+        <is>
+          <t>2-3 days</t>
+        </is>
+      </c>
+      <c r="AB144" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AC144" s="2" t="inlineStr">
+        <is>
+          <t>81-100%</t>
+        </is>
+      </c>
+      <c r="AD144" s="2" t="inlineStr">
+        <is>
+          <t>1-2 weeks</t>
+        </is>
+      </c>
+      <c r="AE144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF144" s="2" t="inlineStr">
+        <is>
+          <t>e-Office, PFMS</t>
+        </is>
+      </c>
+      <c r="AG144" s="2" t="inlineStr">
+        <is>
+          <t>Data entry</t>
+        </is>
+      </c>
+      <c r="AH144" s="2" t="inlineStr">
+        <is>
+          <t>A few share</t>
+        </is>
+      </c>
+      <c r="AI144" s="2" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AJ144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK144" s="2" t="inlineStr">
+        <is>
+          <t>Ask colleague</t>
+        </is>
+      </c>
+      <c r="AL144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM144" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="AN144" s="2" t="inlineStr">
+        <is>
+          <t>Sharing documents</t>
+        </is>
+      </c>
+      <c r="AO144" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ144" s="2" t="inlineStr">
+        <is>
+          <t>Server down during month-end reporting</t>
+        </is>
+      </c>
+      <c r="AR144" s="2" t="inlineStr">
+        <is>
+          <t>Slow internet, Old computers</t>
+        </is>
+      </c>
+      <c r="AS144" s="2" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="AT144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU144" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX144" s="2" t="inlineStr">
+        <is>
+          <t>basic computer operations</t>
+        </is>
+      </c>
+      <c r="AY144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA144" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD144" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE144" s="2" t="inlineStr">
+        <is>
+          <t>1.Training 2.Internet 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF144" s="2" t="inlineStr">
+        <is>
+          <t>Simplified Hindi interface</t>
+        </is>
+      </c>
+      <c r="BG144" s="2" t="inlineStr">
+        <is>
+          <t>Yes significantly</t>
+        </is>
+      </c>
+      <c r="BH144" s="2" t="inlineStr">
+        <is>
+          <t>MP Bhulekh, RCMS</t>
+        </is>
+      </c>
+      <c r="BI144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK144" s="2" t="inlineStr">
+        <is>
+          <t>41-60%</t>
+        </is>
+      </c>
+      <c r="BL144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM144" s="2" t="inlineStr">
+        <is>
+          <t>Mutation backlog exists due to server errors</t>
+        </is>
+      </c>
+      <c r="BN144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG144" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CH144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI144" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>R144</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Reader to Collector / Class III</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>6-10</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>Strongly agree</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q145" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V145" s="3" t="inlineStr">
+        <is>
+          <t>desktop, laptop, phone</t>
+        </is>
+      </c>
+      <c r="W145" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X145" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y145" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="Z145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA145" s="3" t="inlineStr">
+        <is>
+          <t>Same day</t>
+        </is>
+      </c>
+      <c r="AB145" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AC145" s="3" t="inlineStr">
+        <is>
+          <t>81-100%</t>
+        </is>
+      </c>
+      <c r="AD145" s="3" t="inlineStr">
+        <is>
+          <t>&lt;1 day</t>
+        </is>
+      </c>
+      <c r="AE145" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF145" s="3" t="inlineStr">
+        <is>
+          <t>e-Office, email, MS Office</t>
+        </is>
+      </c>
+      <c r="AG145" s="3" t="inlineStr">
+        <is>
+          <t>Data entry</t>
+        </is>
+      </c>
+      <c r="AH145" s="3" t="inlineStr">
+        <is>
+          <t>Everyone does own</t>
+        </is>
+      </c>
+      <c r="AI145" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AJ145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK145" s="3" t="inlineStr">
+        <is>
+          <t>Ask colleague</t>
+        </is>
+      </c>
+      <c r="AL145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM145" s="3" t="inlineStr">
+        <is>
+          <t>WhatsApp, Google Docs, ChatGPT/AI</t>
+        </is>
+      </c>
+      <c r="AN145" s="3" t="inlineStr">
+        <is>
+          <t>Drafting, translating, coordinating</t>
+        </is>
+      </c>
+      <c r="AO145" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ145" s="3" t="inlineStr">
+        <is>
+          <t>Security of official data on personal phone</t>
+        </is>
+      </c>
+      <c r="AR145" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet, Portal crashes</t>
+        </is>
+      </c>
+      <c r="AS145" s="3" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="AT145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU145" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV145" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW145" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX145" s="3" t="inlineStr">
+        <is>
+          <t>advanced Excel, e-Office</t>
+        </is>
+      </c>
+      <c r="AY145" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA145" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE145" s="3" t="inlineStr">
+        <is>
+          <t>1.Training 2.Internet 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF145" s="3" t="inlineStr">
+        <is>
+          <t>Stable internet connectivity</t>
+        </is>
+      </c>
+      <c r="BG145" s="3" t="inlineStr">
+        <is>
+          <t>Yes significantly</t>
+        </is>
+      </c>
+      <c r="BH145" s="3" t="inlineStr">
+        <is>
+          <t>MP Bhulekh, RCMS, SAMPADA 2.0</t>
+        </is>
+      </c>
+      <c r="BI145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK145" s="3" t="inlineStr">
+        <is>
+          <t>21-40%</t>
+        </is>
+      </c>
+      <c r="BL145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM145" s="3" t="inlineStr">
+        <is>
+          <t>Online mutation is faster</t>
+        </is>
+      </c>
+      <c r="BN145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CF145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG145" s="3" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="CH145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI145" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>R145</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Upper Collector / Class I</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>46-60</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>21+</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Grad</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>Strongly agree</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V146" s="2" t="inlineStr">
+        <is>
+          <t>desktop, laptop, phone</t>
+        </is>
+      </c>
+      <c r="W146" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y146" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="Z146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA146" s="2" t="inlineStr">
+        <is>
+          <t>Same day</t>
+        </is>
+      </c>
+      <c r="AB146" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AC146" s="2" t="inlineStr">
+        <is>
+          <t>81-100%</t>
+        </is>
+      </c>
+      <c r="AD146" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1 day</t>
+        </is>
+      </c>
+      <c r="AE146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF146" s="2" t="inlineStr">
+        <is>
+          <t>e-Office, email, MS Office</t>
+        </is>
+      </c>
+      <c r="AG146" s="2" t="inlineStr">
+        <is>
+          <t>Review/approve</t>
+        </is>
+      </c>
+      <c r="AH146" s="2" t="inlineStr">
+        <is>
+          <t>Everyone does own</t>
+        </is>
+      </c>
+      <c r="AI146" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AJ146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK146" s="2" t="inlineStr">
+        <is>
+          <t>Fix myself</t>
+        </is>
+      </c>
+      <c r="AL146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM146" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp, Google Drive</t>
+        </is>
+      </c>
+      <c r="AN146" s="2" t="inlineStr">
+        <is>
+          <t>Coordinating, sharing files</t>
+        </is>
+      </c>
+      <c r="AO146" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ146" s="2" t="inlineStr">
+        <is>
+          <t>Need official communication platform to replace WhatsApp for sensitive data</t>
+        </is>
+      </c>
+      <c r="AR146" s="2" t="inlineStr">
+        <is>
+          <t>Slow internet, Portal crashes</t>
+        </is>
+      </c>
+      <c r="AS146" s="2" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="AT146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX146" s="2" t="inlineStr">
+        <is>
+          <t>e-Office</t>
+        </is>
+      </c>
+      <c r="AY146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA146" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD146" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE146" s="2" t="inlineStr">
+        <is>
+          <t>1.Internet 2.Training 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF146" s="2" t="inlineStr">
+        <is>
+          <t>Stable internet connectivity</t>
+        </is>
+      </c>
+      <c r="BG146" s="2" t="inlineStr">
+        <is>
+          <t>Yes significantly</t>
+        </is>
+      </c>
+      <c r="BH146" s="2" t="inlineStr">
+        <is>
+          <t>MP Bhulekh, RCMS, SAMPADA 2.0</t>
+        </is>
+      </c>
+      <c r="BI146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK146" s="2" t="inlineStr">
+        <is>
+          <t>21-40%</t>
+        </is>
+      </c>
+      <c r="BL146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM146" s="2" t="inlineStr">
+        <is>
+          <t>Online mutation is faster</t>
+        </is>
+      </c>
+      <c r="BN146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG146" s="2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="CH146" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI146" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>R146</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Stenographer / Class III</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>11-20</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>Grad</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>Agree somewhat</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V147" s="3" t="inlineStr">
+        <is>
+          <t>desktop, phone</t>
+        </is>
+      </c>
+      <c r="W147" s="3" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="X147" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y147" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="Z147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA147" s="3" t="inlineStr">
+        <is>
+          <t>2-3 days</t>
+        </is>
+      </c>
+      <c r="AB147" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AC147" s="3" t="inlineStr">
+        <is>
+          <t>81-100%</t>
+        </is>
+      </c>
+      <c r="AD147" s="3" t="inlineStr">
+        <is>
+          <t>1-2 weeks</t>
+        </is>
+      </c>
+      <c r="AE147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF147" s="3" t="inlineStr">
+        <is>
+          <t>e-Office, PFMS</t>
+        </is>
+      </c>
+      <c r="AG147" s="3" t="inlineStr">
+        <is>
+          <t>Data entry</t>
+        </is>
+      </c>
+      <c r="AH147" s="3" t="inlineStr">
+        <is>
+          <t>A few share</t>
+        </is>
+      </c>
+      <c r="AI147" s="3" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AJ147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK147" s="3" t="inlineStr">
+        <is>
+          <t>Ask colleague</t>
+        </is>
+      </c>
+      <c r="AL147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM147" s="3" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="AN147" s="3" t="inlineStr">
+        <is>
+          <t>Communication, typing</t>
+        </is>
+      </c>
+      <c r="AO147" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ147" s="3" t="inlineStr">
+        <is>
+          <t>Security of official data on personal phone</t>
+        </is>
+      </c>
+      <c r="AR147" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet, Old computers</t>
+        </is>
+      </c>
+      <c r="AS147" s="3" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="AT147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU147" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV147" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW147" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX147" s="3" t="inlineStr">
+        <is>
+          <t>Hindi typing, e-Office</t>
+        </is>
+      </c>
+      <c r="AY147" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA147" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD147" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE147" s="3" t="inlineStr">
+        <is>
+          <t>1.Training 2.Internet 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF147" s="3" t="inlineStr">
+        <is>
+          <t>Simplified Hindi interface</t>
+        </is>
+      </c>
+      <c r="BG147" s="3" t="inlineStr">
+        <is>
+          <t>Yes significantly</t>
+        </is>
+      </c>
+      <c r="BH147" s="3" t="inlineStr">
+        <is>
+          <t>MP Bhulekh, RCMS</t>
+        </is>
+      </c>
+      <c r="BI147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK147" s="3" t="inlineStr">
+        <is>
+          <t>41-60%</t>
+        </is>
+      </c>
+      <c r="BL147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM147" s="3" t="inlineStr">
+        <is>
+          <t>Mutation backlog exists due to server errors</t>
+        </is>
+      </c>
+      <c r="BN147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF147" s="3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="CG147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH147" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI147" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>R147</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Reader / Class III</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>6-10</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Grad</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>Agree somewhat</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V148" s="2" t="inlineStr">
+        <is>
+          <t>desktop, phone</t>
+        </is>
+      </c>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="X148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y148" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="Z148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA148" s="2" t="inlineStr">
+        <is>
+          <t>2-3 days</t>
+        </is>
+      </c>
+      <c r="AB148" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AC148" s="2" t="inlineStr">
+        <is>
+          <t>81-100%</t>
+        </is>
+      </c>
+      <c r="AD148" s="2" t="inlineStr">
+        <is>
+          <t>1-2 weeks</t>
+        </is>
+      </c>
+      <c r="AE148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF148" s="2" t="inlineStr">
+        <is>
+          <t>e-Office, PFMS</t>
+        </is>
+      </c>
+      <c r="AG148" s="2" t="inlineStr">
+        <is>
+          <t>Data entry</t>
+        </is>
+      </c>
+      <c r="AH148" s="2" t="inlineStr">
+        <is>
+          <t>A few share</t>
+        </is>
+      </c>
+      <c r="AI148" s="2" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AJ148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK148" s="2" t="inlineStr">
+        <is>
+          <t>Ask colleague</t>
+        </is>
+      </c>
+      <c r="AL148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM148" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="AN148" s="2" t="inlineStr">
+        <is>
+          <t>Sharing documents, communication</t>
+        </is>
+      </c>
+      <c r="AO148" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ148" s="2" t="inlineStr">
+        <is>
+          <t>Security of official data on personal phone</t>
+        </is>
+      </c>
+      <c r="AR148" s="2" t="inlineStr">
+        <is>
+          <t>Slow internet, Old computers</t>
+        </is>
+      </c>
+      <c r="AS148" s="2" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="AT148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX148" s="2" t="inlineStr">
+        <is>
+          <t>basic computer operations, e-Office</t>
+        </is>
+      </c>
+      <c r="AY148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA148" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD148" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE148" s="2" t="inlineStr">
+        <is>
+          <t>1.Training 2.Internet 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF148" s="2" t="inlineStr">
+        <is>
+          <t>Simplified Hindi interface</t>
+        </is>
+      </c>
+      <c r="BG148" s="2" t="inlineStr">
+        <is>
+          <t>Yes significantly</t>
+        </is>
+      </c>
+      <c r="BH148" s="2" t="inlineStr">
+        <is>
+          <t>MP Bhulekh, RCMS</t>
+        </is>
+      </c>
+      <c r="BI148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK148" s="2" t="inlineStr">
+        <is>
+          <t>41-60%</t>
+        </is>
+      </c>
+      <c r="BL148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM148" s="2" t="inlineStr">
+        <is>
+          <t>Mutation backlog exists due to server errors</t>
+        </is>
+      </c>
+      <c r="BN148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF148" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CG148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI148" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>R148</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Support Staff (Class IV) / Class IV</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>11-20</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>Yes, somewhat</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q149" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S149" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U149" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V149" s="3" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="W149" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X149" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y149" s="3" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
+      <c r="Z149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB149" s="3" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
+      <c r="AC149" s="3" t="inlineStr">
+        <is>
+          <t>0-20%</t>
+        </is>
+      </c>
+      <c r="AD149" s="3" t="inlineStr">
+        <is>
+          <t>&gt;2 weeks</t>
+        </is>
+      </c>
+      <c r="AE149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG149" s="3" t="inlineStr">
+        <is>
+          <t>Don't use</t>
+        </is>
+      </c>
+      <c r="AH149" s="3" t="inlineStr">
+        <is>
+          <t>Yes one person</t>
+        </is>
+      </c>
+      <c r="AI149" s="3" t="inlineStr">
+        <is>
+          <t>Rely on subordinates</t>
+        </is>
+      </c>
+      <c r="AJ149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK149" s="3" t="inlineStr">
+        <is>
+          <t>Wait for IT</t>
+        </is>
+      </c>
+      <c r="AL149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM149" s="3" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="AN149" s="3" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="AO149" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ149" s="3" t="inlineStr">
+        <is>
+          <t>Only know WhatsApp, need training in local language</t>
+        </is>
+      </c>
+      <c r="AR149" s="3" t="inlineStr">
+        <is>
+          <t>No device, No training, Complex UI</t>
+        </is>
+      </c>
+      <c r="AS149" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AT149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AX149" s="3" t="inlineStr">
+        <is>
+          <t>basic smartphone usage</t>
+        </is>
+      </c>
+      <c r="AZ149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA149" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD149" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE149" s="3" t="inlineStr">
+        <is>
+          <t>1.Training 2.Hindi UI 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF149" s="3" t="inlineStr">
+        <is>
+          <t>Basic training in Hindi</t>
+        </is>
+      </c>
+      <c r="BG149" s="3" t="inlineStr">
+        <is>
+          <t>Can't say</t>
+        </is>
+      </c>
+      <c r="CA149" s="3" t="inlineStr">
+        <is>
+          <t>ANMOL MP</t>
+        </is>
+      </c>
+      <c r="CB149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD149" s="3" t="inlineStr">
+        <is>
+          <t>Open register first, note patient details, enter on phone later</t>
+        </is>
+      </c>
+      <c r="CF149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH149" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CI149" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>R149</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Support Staff (Class IV) / Class IV</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>46-60</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>21+</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q150" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" s="2" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y150" s="2" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+      <c r="Z150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB150" s="2" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+      <c r="AC150" s="2" t="inlineStr">
+        <is>
+          <t>0-20%</t>
+        </is>
+      </c>
+      <c r="AD150" s="2" t="inlineStr">
+        <is>
+          <t>&gt;2 weeks</t>
+        </is>
+      </c>
+      <c r="AE150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG150" s="2" t="inlineStr">
+        <is>
+          <t>Don't use</t>
+        </is>
+      </c>
+      <c r="AH150" s="2" t="inlineStr">
+        <is>
+          <t>Yes one person</t>
+        </is>
+      </c>
+      <c r="AI150" s="2" t="inlineStr">
+        <is>
+          <t>Rely on subordinates</t>
+        </is>
+      </c>
+      <c r="AJ150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK150" s="2" t="inlineStr">
+        <is>
+          <t>Wait for IT</t>
+        </is>
+      </c>
+      <c r="AL150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM150" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AN150" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AO150" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ150" s="2" t="inlineStr">
+        <is>
+          <t>Only know WhatsApp, need training in local language</t>
+        </is>
+      </c>
+      <c r="AR150" s="2" t="inlineStr">
+        <is>
+          <t>No device, No training, Complex UI</t>
+        </is>
+      </c>
+      <c r="AS150" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AT150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AX150" s="2" t="inlineStr">
+        <is>
+          <t>basic computer operations</t>
+        </is>
+      </c>
+      <c r="AZ150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA150" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD150" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE150" s="2" t="inlineStr">
+        <is>
+          <t>1.Training 2.Hindi UI 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF150" s="2" t="inlineStr">
+        <is>
+          <t>Basic training in Hindi</t>
+        </is>
+      </c>
+      <c r="BG150" s="2" t="inlineStr">
+        <is>
+          <t>Can't say</t>
+        </is>
+      </c>
+      <c r="CA150" s="2" t="inlineStr">
+        <is>
+          <t>ANMOL MP</t>
+        </is>
+      </c>
+      <c r="CB150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CC150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD150" s="2" t="inlineStr">
+        <is>
+          <t>Write on paper, cannot enter on mobile</t>
+        </is>
+      </c>
+      <c r="CF150" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CG150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI150" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>R150</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Support Staff (Class IV) / Class IV</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>46-60</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>21+</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q151" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S151" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T151" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" s="3" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="W151" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X151" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y151" s="3" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+      <c r="Z151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB151" s="3" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+      <c r="AC151" s="3" t="inlineStr">
+        <is>
+          <t>0-20%</t>
+        </is>
+      </c>
+      <c r="AD151" s="3" t="inlineStr">
+        <is>
+          <t>&gt;2 weeks</t>
+        </is>
+      </c>
+      <c r="AE151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG151" s="3" t="inlineStr">
+        <is>
+          <t>Don't use</t>
+        </is>
+      </c>
+      <c r="AH151" s="3" t="inlineStr">
+        <is>
+          <t>Yes one person</t>
+        </is>
+      </c>
+      <c r="AI151" s="3" t="inlineStr">
+        <is>
+          <t>Rely on subordinates</t>
+        </is>
+      </c>
+      <c r="AJ151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK151" s="3" t="inlineStr">
+        <is>
+          <t>Wait for IT</t>
+        </is>
+      </c>
+      <c r="AL151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AN151" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AO151" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ151" s="3" t="inlineStr">
+        <is>
+          <t>Only know WhatsApp, need training in local language</t>
+        </is>
+      </c>
+      <c r="AR151" s="3" t="inlineStr">
+        <is>
+          <t>No device, No training, Complex UI</t>
+        </is>
+      </c>
+      <c r="AS151" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AT151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU151" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AX151" s="3" t="inlineStr">
+        <is>
+          <t>basic computer operations</t>
+        </is>
+      </c>
+      <c r="AZ151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA151" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB151" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC151" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD151" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE151" s="3" t="inlineStr">
+        <is>
+          <t>1.Training 2.Hindi UI 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF151" s="3" t="inlineStr">
+        <is>
+          <t>Basic training in Hindi</t>
+        </is>
+      </c>
+      <c r="BG151" s="3" t="inlineStr">
+        <is>
+          <t>Can't say</t>
+        </is>
+      </c>
+      <c r="CA151" s="3" t="inlineStr">
+        <is>
+          <t>ANMOL MP</t>
+        </is>
+      </c>
+      <c r="CB151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CC151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD151" s="3" t="inlineStr">
+        <is>
+          <t>Write on paper, cannot enter on mobile</t>
+        </is>
+      </c>
+      <c r="CF151" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CG151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH151" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI151" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>R151</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Support Staff (Class IV) / Class IV</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>46-60</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>21+</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q152" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V152" s="2" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y152" s="2" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+      <c r="Z152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB152" s="2" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+      <c r="AC152" s="2" t="inlineStr">
+        <is>
+          <t>0-20%</t>
+        </is>
+      </c>
+      <c r="AD152" s="2" t="inlineStr">
+        <is>
+          <t>&gt;2 weeks</t>
+        </is>
+      </c>
+      <c r="AE152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG152" s="2" t="inlineStr">
+        <is>
+          <t>Don't use</t>
+        </is>
+      </c>
+      <c r="AH152" s="2" t="inlineStr">
+        <is>
+          <t>Yes one person</t>
+        </is>
+      </c>
+      <c r="AI152" s="2" t="inlineStr">
+        <is>
+          <t>Rely on subordinates</t>
+        </is>
+      </c>
+      <c r="AJ152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK152" s="2" t="inlineStr">
+        <is>
+          <t>Wait for IT</t>
+        </is>
+      </c>
+      <c r="AL152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM152" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AN152" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AO152" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ152" s="2" t="inlineStr">
+        <is>
+          <t>Only know WhatsApp, need training in local language</t>
+        </is>
+      </c>
+      <c r="AR152" s="2" t="inlineStr">
+        <is>
+          <t>No device, No training, Complex UI</t>
+        </is>
+      </c>
+      <c r="AS152" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AT152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AX152" s="2" t="inlineStr">
+        <is>
+          <t>basic computer operations</t>
+        </is>
+      </c>
+      <c r="AZ152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA152" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD152" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE152" s="2" t="inlineStr">
+        <is>
+          <t>1.Training 2.Hindi UI 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF152" s="2" t="inlineStr">
+        <is>
+          <t>Basic training in Hindi</t>
+        </is>
+      </c>
+      <c r="BG152" s="2" t="inlineStr">
+        <is>
+          <t>Can't say</t>
+        </is>
+      </c>
+      <c r="CA152" s="2" t="inlineStr">
+        <is>
+          <t>ANMOL MP</t>
+        </is>
+      </c>
+      <c r="CB152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CC152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD152" s="2" t="inlineStr">
+        <is>
+          <t>Write on paper, cannot enter on mobile</t>
+        </is>
+      </c>
+      <c r="CF152" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CG152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI152" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>R152</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Support Staff (Class IV) / Class IV</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>46-60</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>21+</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q153" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" s="3" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="W153" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y153" s="3" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+      <c r="Z153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB153" s="3" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+      <c r="AC153" s="3" t="inlineStr">
+        <is>
+          <t>0-20%</t>
+        </is>
+      </c>
+      <c r="AD153" s="3" t="inlineStr">
+        <is>
+          <t>&gt;2 weeks</t>
+        </is>
+      </c>
+      <c r="AE153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG153" s="3" t="inlineStr">
+        <is>
+          <t>Don't use</t>
+        </is>
+      </c>
+      <c r="AH153" s="3" t="inlineStr">
+        <is>
+          <t>Yes one person</t>
+        </is>
+      </c>
+      <c r="AI153" s="3" t="inlineStr">
+        <is>
+          <t>Rely on subordinates</t>
+        </is>
+      </c>
+      <c r="AJ153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK153" s="3" t="inlineStr">
+        <is>
+          <t>Wait for IT</t>
+        </is>
+      </c>
+      <c r="AL153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM153" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AN153" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AO153" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ153" s="3" t="inlineStr">
+        <is>
+          <t>Only know WhatsApp, need training in local language</t>
+        </is>
+      </c>
+      <c r="AR153" s="3" t="inlineStr">
+        <is>
+          <t>No device, No training, Complex UI</t>
+        </is>
+      </c>
+      <c r="AS153" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AT153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AX153" s="3" t="inlineStr">
+        <is>
+          <t>basic computer operations</t>
+        </is>
+      </c>
+      <c r="AZ153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA153" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD153" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE153" s="3" t="inlineStr">
+        <is>
+          <t>1.Training 2.Hindi UI 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF153" s="3" t="inlineStr">
+        <is>
+          <t>Basic training in Hindi</t>
+        </is>
+      </c>
+      <c r="BG153" s="3" t="inlineStr">
+        <is>
+          <t>Can't say</t>
+        </is>
+      </c>
+      <c r="CA153" s="3" t="inlineStr">
+        <is>
+          <t>ANMOL MP</t>
+        </is>
+      </c>
+      <c r="CB153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CC153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD153" s="3" t="inlineStr">
+        <is>
+          <t>Write on paper, cannot enter on mobile</t>
+        </is>
+      </c>
+      <c r="CF153" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CG153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI153" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>R153</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Support Staff (Class IV) / Class IV</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>6-10</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>Yes, strongly agree</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q154" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V154" s="2" t="inlineStr">
+        <is>
+          <t>phone, laptop</t>
+        </is>
+      </c>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y154" s="2" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
+      <c r="Z154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA154" s="2" t="inlineStr">
+        <is>
+          <t>2-3 days</t>
+        </is>
+      </c>
+      <c r="AB154" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AC154" s="2" t="inlineStr">
+        <is>
+          <t>41-60%</t>
+        </is>
+      </c>
+      <c r="AD154" s="2" t="inlineStr">
+        <is>
+          <t>Few days</t>
+        </is>
+      </c>
+      <c r="AE154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF154" s="2" t="inlineStr">
+        <is>
+          <t>e-Office, email</t>
+        </is>
+      </c>
+      <c r="AG154" s="2" t="inlineStr">
+        <is>
+          <t>Data entry</t>
+        </is>
+      </c>
+      <c r="AH154" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AI154" s="2" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AJ154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK154" s="2" t="inlineStr">
+        <is>
+          <t>Ask colleague</t>
+        </is>
+      </c>
+      <c r="AL154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM154" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp, Google Docs, YouTube</t>
+        </is>
+      </c>
+      <c r="AN154" s="2" t="inlineStr">
+        <is>
+          <t>Drafting, coordinates, learning</t>
+        </is>
+      </c>
+      <c r="AO154" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ154" s="2" t="inlineStr">
+        <is>
+          <t>Data security concerns with personal devices</t>
+        </is>
+      </c>
+      <c r="AR154" s="2" t="inlineStr">
+        <is>
+          <t>Slow internet, Old computers</t>
+        </is>
+      </c>
+      <c r="AS154" s="2" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="AT154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU154" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX154" s="2" t="inlineStr">
+        <is>
+          <t>advanced software operations</t>
+        </is>
+      </c>
+      <c r="AY154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA154" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE154" s="2" t="inlineStr">
+        <is>
+          <t>1.Training 2.Internet 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF154" s="2" t="inlineStr">
+        <is>
+          <t>Stable internet connectivity</t>
+        </is>
+      </c>
+      <c r="BG154" s="2" t="inlineStr">
+        <is>
+          <t>Yes significantly</t>
+        </is>
+      </c>
+      <c r="CA154" s="2" t="inlineStr">
+        <is>
+          <t>ANMOL MP, eVIN</t>
+        </is>
+      </c>
+      <c r="CB154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CC154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CD154" s="2" t="inlineStr">
+        <is>
+          <t>Open ANMOL app, enter details of ANC visit, check sync status, confirm upload</t>
+        </is>
+      </c>
+      <c r="CF154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG154" s="2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="CH154" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CI154" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>R154</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Support Staff (Class IV) / Class IV</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>6-10</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>Yes, strongly agree</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N155" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O155" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P155" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R155" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T155" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V155" s="3" t="inlineStr">
+        <is>
+          <t>desktop, phone, laptop</t>
+        </is>
+      </c>
+      <c r="W155" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X155" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y155" s="3" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
+      <c r="Z155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA155" s="3" t="inlineStr">
+        <is>
+          <t>Same day</t>
+        </is>
+      </c>
+      <c r="AB155" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AC155" s="3" t="inlineStr">
+        <is>
+          <t>61-80%</t>
+        </is>
+      </c>
+      <c r="AD155" s="3" t="inlineStr">
+        <is>
+          <t>&lt;1 day</t>
+        </is>
+      </c>
+      <c r="AE155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF155" s="3" t="inlineStr">
+        <is>
+          <t>e-Office, email, MS Office</t>
+        </is>
+      </c>
+      <c r="AG155" s="3" t="inlineStr">
+        <is>
+          <t>Data entry</t>
+        </is>
+      </c>
+      <c r="AH155" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AI155" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AJ155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK155" s="3" t="inlineStr">
+        <is>
+          <t>Fix myself</t>
+        </is>
+      </c>
+      <c r="AL155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM155" s="3" t="inlineStr">
+        <is>
+          <t>WhatsApp, Google Sheets, ChatGPT/AI</t>
+        </is>
+      </c>
+      <c r="AN155" s="3" t="inlineStr">
+        <is>
+          <t>Data entry, spreadsheet formulas, reporting</t>
+        </is>
+      </c>
+      <c r="AO155" s="3" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="AP155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ155" s="3" t="inlineStr">
+        <is>
+          <t>Security of official data on personal phone</t>
+        </is>
+      </c>
+      <c r="AR155" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet, Portal crashes</t>
+        </is>
+      </c>
+      <c r="AS155" s="3" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="AT155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU155" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX155" s="3" t="inlineStr">
+        <is>
+          <t>data security, database management</t>
+        </is>
+      </c>
+      <c r="AY155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA155" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BB155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE155" s="3" t="inlineStr">
+        <is>
+          <t>1.Training 2.Internet 3.Devices</t>
+        </is>
+      </c>
+      <c r="BF155" s="3" t="inlineStr">
+        <is>
+          <t>Stable internet connectivity</t>
+        </is>
+      </c>
+      <c r="BG155" s="3" t="inlineStr">
+        <is>
+          <t>Yes significantly</t>
+        </is>
+      </c>
+      <c r="CA155" s="3" t="inlineStr">
+        <is>
+          <t>ANMOL MP, eVIN, HMIS</t>
+        </is>
+      </c>
+      <c r="CB155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CC155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CD155" s="3" t="inlineStr">
+        <is>
+          <t>Open ANMOL app, enter details of ANC visit, check sync status, confirm upload</t>
+        </is>
+      </c>
+      <c r="CF155" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CG155" s="3" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="CH155" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CI155" s="3" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CD141"/>
+  <autoFilter ref="A1:CI155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40335,7 +44127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -41236,6 +45028,60 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q78_ANMOL_ABHA</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Q78: ANMOL / ABHA usability</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>1-5 Likert (Health)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Q79_IHIP_workload</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Q79: IHIP workload integration</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>1-5 Likert (Health)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Numeric</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
